--- a/medical_consent_forms/008_telehealth_services_agreement_form--medical_consent_forms.xlsx
+++ b/medical_consent_forms/008_telehealth_services_agreement_form--medical_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,89 +525,105 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telehealth Services Agreement Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your full name.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>telehealth_services_agreement_1</t>
+          <t>patient_date_of_birth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Patient Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your date of birth?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_telehealth_agreement</t>
+          <t>telehealth_services_method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Patient Telehealth Agreement</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your preferred contact method for telehealth services?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select your preferred contact method.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_medical_history</t>
+          <t>patient_age_verification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Patient Medical History</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Are you 18 years or older?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Patient Medical History</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your medical history (e.g., allergies, conditions, medications)?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide a detailed list.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,36 +660,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Patient Consent to Share</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Do you consent to share your medical history with our team?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_consent_to_share</t>
+          <t>patient_contact_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patient Consent to Share</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Do you have any emergency contact information (e.g., family member or caregiver)?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>patient_contact_info</t>
+          <t>patient_contact_info_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patient Contact Info</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have any emergency contact phone numbers?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide numbers separated by commas.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +736,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_contact_info</t>
+          <t>patient_contact_info_address</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Patient Contact Info</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have any emergency contact addresses?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide addresses separated by commas.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_medical_history</t>
+          <t>patient_contact_info_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patient Medical History</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What are your emergency contact names?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide names separated by commas.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,64 +790,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>patient_medical_history</t>
+          <t>patient_medical_conditions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patient Medical History</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Do you have any medical conditions that may impact your ability to participate in telehealth services?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>patient_contact_info</t>
+          <t>patient_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patient Contact Info</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide your email address.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>telehealth_services_agreement_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Telehealth Services Agreement 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,85 +875,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>telehealth_services_agreement_1_choices</t>
+          <t>telehealth_services_method_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>telehealth_services_agreement_1_choices</t>
+          <t>telehealth_services_method_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_telehealth_agreement_choices</t>
+          <t>telehealth_services_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>online</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_telehealth_agreement_choices</t>
+          <t>patient_age_verification_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>patient_consent_to_share_choices</t>
+          <t>patient_age_verification_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -940,12 +965,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -957,95 +982,78 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>patient_consent_to_share_choices</t>
+          <t>patient_contact_info_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>patient_medical_history_choices</t>
+          <t>patient_contact_info_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>patient_medical_history_choices</t>
+          <t>patient_medical_conditions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>telehealth_services_agreement_2_choices</t>
+          <t>patient_medical_conditions_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>telehealth_services_agreement_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
